--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:22:20+00:00</t>
+    <t>2026-09-04T10:10:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:10:30+00:00</t>
+    <t>2026-09-04T12:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:54:27+00:00</t>
+    <t>2026-09-07T07:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:40:03+00:00</t>
+    <t>2026-09-07T15:13:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
